--- a/artfynd/A 412-2023 artfynd.xlsx
+++ b/artfynd/A 412-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 412-2023 artfynd.xlsx
+++ b/artfynd/A 412-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>439681</v>
       </c>
       <c r="B2" t="n">
-        <v>87979</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462812.4530066749</v>
+        <v>462812</v>
       </c>
       <c r="R2" t="n">
-        <v>6474774.93317776</v>
+        <v>6474775</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2010-09-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-09-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -801,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1439810</v>
+        <v>585609</v>
       </c>
       <c r="B3" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462707.2571283202</v>
+        <v>462760</v>
       </c>
       <c r="R3" t="n">
-        <v>6474862.902423349</v>
+        <v>6474828</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,24 +854,14 @@
           <t>2010-09-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-09-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>leg. Ewa Lilliesköld,Kurt-Anders Johansson,Rolf-Göran Carlsson. 1 mycel. Koordinater = 1415632 - 6477552,. Stora Röå NR ligger vid Röåsjöns norra sida och är ca 100 ha stort. Området ligger till största del på sand och är tall och granskogs dominerad. Utm</t>
+          <t>leg. Ewa Lilliesköld,Kurt-Anders Johansson,Rolf-Göran Carlsson. 2 mycel . Koordinater = 1415685 - 6477517 och 1415771 - 6477357. Stora Röå NR ligger vid Röåsjöns norra sida och är ca 100 ha stort. Området ligger till största del på sand och är tall och g</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +875,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>tallskog/Stora Röå NR ligger vid Röåsjöns norra sida och är ca 100 ha stort.</t>
+          <t>tallskog på sand/Stora Röå NR ligger vid Röåsjöns norra sida och är ca 100 ha</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>RGC10-066</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,15 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90003779</v>
+        <v>90003776</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462663.9487901878</v>
+        <v>462907</v>
       </c>
       <c r="R4" t="n">
-        <v>6474890.033706346</v>
+        <v>6474640</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,19 +970,9 @@
           <t>2020-09-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,15 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90003780</v>
+        <v>90003777</v>
       </c>
       <c r="B5" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1089,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462758.9686133281</v>
+        <v>462745</v>
       </c>
       <c r="R5" t="n">
-        <v>6474836.215727894</v>
+        <v>6474866</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1122,19 +1077,9 @@
           <t>2020-09-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,37 +1116,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>90003776</v>
+        <v>90003779</v>
       </c>
       <c r="B6" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1211,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462907.2360356</v>
+        <v>462664</v>
       </c>
       <c r="R6" t="n">
-        <v>6474639.90765772</v>
+        <v>6474890</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,19 +1184,9 @@
           <t>2020-09-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,6 +1220,472 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>90003783</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>St Röå, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>462807</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6474800</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brevik</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1439810</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stora Röå NR, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>462707</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6474863</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brevik</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2010-09-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2010-09-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>leg. Ewa Lilliesköld,Kurt-Anders Johansson,Rolf-Göran Carlsson. 1 mycel. Koordinater = 1415632 - 6477552,. Stora Röå NR ligger vid Röåsjöns norra sida och är ca 100 ha stort. Området ligger till största del på sand och är tall och granskogs dominerad. Utm</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>tallskog/Stora Röå NR ligger vid Röåsjöns norra sida och är ca 100 ha stort.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Ewa Grunditz Lilliesköld</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>VBSK fynddatabas</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>90003780</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>St Röå, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>462759</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6474836</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brevik</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-09-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emma Roland</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emma Roland, Helena Bager</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Sandbarrskog Västra Götaland</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>84427133</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Röåsjön, Breviks distrikt, Hjo, Hjo kommun, Götaland, Västra Götalands län, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>462717</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6474869</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brevik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-04-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-04-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>50st längs stigen på en sträcka av 500m. Parning. Vilande.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Wenäll</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Wenäll</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 412-2023 artfynd.xlsx
+++ b/artfynd/A 412-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>VBSK fynddatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/439681</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>VBSK fynddatabas</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/585609</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003776</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003777</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003779</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003783</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
           <t>VBSK fynddatabas</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1439810</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90003780</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1686,8 +1731,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84427133</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>